--- a/FichierControleFluxCoteUnix/rapport/11082026_FOURNISSEUR_CEC.xlsx
+++ b/FichierControleFluxCoteUnix/rapport/11082026_FOURNISSEUR_CEC.xlsx
@@ -11,12 +11,20 @@
     <sheet name="Factures a 0" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Synthese Oracle" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Detail Oracle" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Synthese 110826-200457" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Factures a 0 110826-200457" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Synthese Oracle 110826-200457" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Detail Oracle 110826-200457" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Synthese'!$A$6:$F$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Factures a 0'!$A$4:$D$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Synthese Oracle'!$A$4:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Detail Oracle'!$A$4:$G$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Synthese 110826-200457'!$A$6:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Factures a 0 110826-200457'!$A$4:$D$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Synthese Oracle 110826-200457'!$A$4:$I$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Detail Oracle 110826-200457'!$A$4:$G$166</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -762,14 +770,6 @@
           <t>CONTROLE FAC02 FOURNISSEURS - SYNTHESE ORACLE PAR FOLIO</t>
         </is>
       </c>
-      <c r="B1" s="13" t="n"/>
-      <c r="C1" s="13" t="n"/>
-      <c r="D1" s="13" t="n"/>
-      <c r="E1" s="13" t="n"/>
-      <c r="F1" s="13" t="n"/>
-      <c r="G1" s="13" t="n"/>
-      <c r="H1" s="13" t="n"/>
-      <c r="I1" s="13" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -963,17 +963,5543 @@
           <t>CONTROLE FAC02 FOURNISSEURS - DETAIL FACTURE PAR FACTURE</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Fichier : CEL01_SRC_FACTURESFOURNISSEURS_110826-200457_ST_CEL01_639220754971423753_001  |  Execution : 25/08/2026 20:38:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Folio</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Numero Piece</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Date Piece</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Montant Fichier</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Montant Oracle</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Montant Interface</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>40695517S</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>5173.73</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>5173.73</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>5173.73</v>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>10257478482</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>483.52</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>483.52</v>
+      </c>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>2026103117629</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>7721.26</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>7721.26</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>7721.26</v>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>2026103117630</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>1137.92</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>1137.92</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>1137.92</v>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>100005419318</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>100005422908</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>91.42</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>91.42</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>91.42</v>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>100005422904</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>91.42</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>91.42</v>
+      </c>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>26-f07</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>8112.75</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>8112.75</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>8112.75</v>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>31FAC2608-001143</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>66353</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>66353</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>66353</v>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>268041190</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>2060.63</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>2060.63</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>2060.63</v>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>268041189</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>3037.15</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>3037.15</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>3037.15</v>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>1275951E</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>22706.64</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>22706.64</v>
+      </c>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>26073211</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>1328.13</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>1328.13</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>1328.13</v>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>2311902G</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>1068644461</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>16820.05</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>16820.05</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>16820.05</v>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>2311903G</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>321.01</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>321.01</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>321.01</v>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>2311942G</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>374.88</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>374.88</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>374.88</v>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>202608ANE0263</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>1593.48</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>1593.48</v>
+      </c>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>2312221G</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>653.1799999999999</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>653.1799999999999</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>653.1799999999999</v>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>2312234G</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>377.59</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>377.59</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>377.59</v>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>202608ANE0248</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>2579.77</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>2579.77</v>
+      </c>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>2312236G</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>24.08</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>24.08</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>24.08</v>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>2311901G</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>-13.48</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>-13.48</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>-13.48</v>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>2026-009 / 2618608</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>142.64</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>142.64</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>142.64</v>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>100005464408</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>91.42</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>91.42</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>91.42</v>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>100005464459</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>202608ANE0258</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>1314.92</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>1314.92</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>1314.92</v>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>100005430057</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>141.04</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>141.04</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>141.04</v>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>202608ANE0251</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>2091.63</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>2091.63</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>2091.63</v>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>100005464412</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>72.04000000000001</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>72.04000000000001</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>72.04000000000001</v>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>202608ANE0249</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>3130.85</v>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>3130.85</v>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>3130.85</v>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>100005464419</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>100005464426</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="E37" s="7" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>202608ANE0250</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>3061.71</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>3061.71</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>3061.71</v>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>100005464424</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="E39" s="7" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>100005406798</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>2412.22</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>2412.22</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>2412.22</v>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>100005464454</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>91.42</v>
+      </c>
+      <c r="E41" s="7" t="n">
+        <v>91.42</v>
+      </c>
+      <c r="F41" s="7" t="n">
+        <v>91.42</v>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>202608ANE0255</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>1587.87</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>1587.87</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>1587.87</v>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>100005406800</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>2434.12</v>
+      </c>
+      <c r="E43" s="7" t="n">
+        <v>2434.12</v>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>2434.12</v>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>FO202600125355</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>2273.45</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>2273.45</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>2273.45</v>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>660000716821</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>2541.25</v>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>2541.25</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>2541.25</v>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>10257637489</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>3038.08</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>3038.08</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>3038.08</v>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>W4FCF26070016</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>2473.86</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>2473.86</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>2473.86</v>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>202607XI01512</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="n">
+        <v>7437.48</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>7437.48</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>7437.48</v>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>202607XI01522</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>455.71</v>
+      </c>
+      <c r="E49" s="7" t="n">
+        <v>455.71</v>
+      </c>
+      <c r="F49" s="7" t="n">
+        <v>455.71</v>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>FA0000109249</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>F00510040</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>5383.08</v>
+      </c>
+      <c r="E51" s="7" t="n">
+        <v>5383.08</v>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>5383.08</v>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>F00510039</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="n">
+        <v>59254.17</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>59254.17</v>
+      </c>
+      <c r="F52" s="10" t="n">
+        <v>59254.17</v>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>C26G538006</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>15304.75</v>
+      </c>
+      <c r="E53" s="7" t="n">
+        <v>15304.75</v>
+      </c>
+      <c r="F53" s="7" t="n">
+        <v>15304.75</v>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>200006726134</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="n">
+        <v>35883.64</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>35883.64</v>
+      </c>
+      <c r="F54" s="10" t="n">
+        <v>35883.64</v>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>D26001612</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>99690.58</v>
+      </c>
+      <c r="E55" s="7" t="n">
+        <v>99690.58</v>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>99690.58</v>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>C26G538029</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="n">
+        <v>8854.34</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>8854.34</v>
+      </c>
+      <c r="F56" s="10" t="n">
+        <v>8854.34</v>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>FO202600108312</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>2370.11</v>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>2370.11</v>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>2370.11</v>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>100005398604</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="n">
+        <v>3231.7</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>3231.7</v>
+      </c>
+      <c r="F58" s="10" t="n">
+        <v>3231.7</v>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>100005429961</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>141.04</v>
+      </c>
+      <c r="E59" s="7" t="n">
+        <v>141.04</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>141.04</v>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>100005447127</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="F60" s="10" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>100005429973</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="E61" s="7" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>100005420408</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="n">
+        <v>576.0700000000001</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>576.0700000000001</v>
+      </c>
+      <c r="F62" s="10" t="n">
+        <v>576.0700000000001</v>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>100005429968</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="E63" s="7" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="F63" s="7" t="n"/>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>100005422905</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="F64" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>100005447117</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="E65" s="7" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="F65" s="7" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="G65" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>100005447126</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="F66" s="10" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="G66" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>100005429974</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="E67" s="7" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="F67" s="7" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>100005428269</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="F68" s="10" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>100005408279</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="E69" s="7" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="F69" s="7" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>100005429959</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="F70" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>100005426593</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>586.2</v>
+      </c>
+      <c r="E71" s="7" t="n">
+        <v>586.2</v>
+      </c>
+      <c r="F71" s="7" t="n">
+        <v>586.2</v>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>100005427615</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="F72" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>1276823E</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>3232.06</v>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>3232.06</v>
+      </c>
+      <c r="F73" s="7" t="n">
+        <v>3232.06</v>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>100005426014</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="n">
+        <v>345.68</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>345.68</v>
+      </c>
+      <c r="F74" s="10" t="n">
+        <v>345.68</v>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>269060107647</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>1469.28</v>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>1469.28</v>
+      </c>
+      <c r="F75" s="7" t="n">
+        <v>1469.28</v>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>100005501408</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="F76" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>100005430009</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="E77" s="7" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="F77" s="7" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>100005427159</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="F78" s="10" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>269060108270</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="n">
+        <v>861.46</v>
+      </c>
+      <c r="E79" s="7" t="n">
+        <v>861.46</v>
+      </c>
+      <c r="F79" s="7" t="n">
+        <v>861.46</v>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>100005504136</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="F80" s="10" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>1107290219</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="n">
+        <v>8752.75</v>
+      </c>
+      <c r="E81" s="7" t="n">
+        <v>8752.75</v>
+      </c>
+      <c r="F81" s="7" t="n">
+        <v>8752.75</v>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>100005464395</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="F82" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>100005429960</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>91.42</v>
+      </c>
+      <c r="E83" s="7" t="n">
+        <v>91.42</v>
+      </c>
+      <c r="F83" s="7" t="n"/>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>100005426580</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="n">
+        <v>677.62</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>677.62</v>
+      </c>
+      <c r="F84" s="10" t="n">
+        <v>677.62</v>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>100005427228</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="E85" s="7" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="F85" s="7" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>100005427567</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="n">
+        <v>625.6900000000001</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>625.6900000000001</v>
+      </c>
+      <c r="F86" s="10" t="n">
+        <v>625.6900000000001</v>
+      </c>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>100005427687</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="n">
+        <v>141.04</v>
+      </c>
+      <c r="E87" s="7" t="n">
+        <v>141.04</v>
+      </c>
+      <c r="F87" s="7" t="n">
+        <v>141.04</v>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>100005427849</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="n">
+        <v>625.6900000000001</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>625.6900000000001</v>
+      </c>
+      <c r="F88" s="10" t="n">
+        <v>625.6900000000001</v>
+      </c>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>100005406799</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="n">
+        <v>926.37</v>
+      </c>
+      <c r="E89" s="7" t="n">
+        <v>926.37</v>
+      </c>
+      <c r="F89" s="7" t="n">
+        <v>926.37</v>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>100005464380</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="F90" s="10" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="G90" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>1981101E</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="n">
+        <v>670.5700000000001</v>
+      </c>
+      <c r="E91" s="7" t="n">
+        <v>670.5700000000001</v>
+      </c>
+      <c r="F91" s="7" t="n">
+        <v>670.5700000000001</v>
+      </c>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>100005464440</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="F92" s="10" t="n"/>
+      <c r="G92" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>100005464446</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="E93" s="7" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="F93" s="7" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>100005464437</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="F94" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>100005464405</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="E95" s="7" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="F95" s="7" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>104006663776</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="n">
+        <v>40811.38</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>40811.38</v>
+      </c>
+      <c r="F96" s="10" t="n">
+        <v>40811.38</v>
+      </c>
+      <c r="G96" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>100005464452</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="E97" s="7" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="F97" s="7" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>100005464450</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="n">
+        <v>91.42</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>91.42</v>
+      </c>
+      <c r="F98" s="10" t="n"/>
+      <c r="G98" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>104006663775</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="n">
+        <v>37668</v>
+      </c>
+      <c r="E99" s="7" t="n">
+        <v>37668</v>
+      </c>
+      <c r="F99" s="7" t="n">
+        <v>37668</v>
+      </c>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>100005464449</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="F100" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>100005447123</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="n">
+        <v>610.54</v>
+      </c>
+      <c r="E101" s="7" t="n">
+        <v>610.54</v>
+      </c>
+      <c r="F101" s="7" t="n">
+        <v>610.54</v>
+      </c>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>102007001060</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="n">
+        <v>3342.61</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>3342.61</v>
+      </c>
+      <c r="F102" s="10" t="n">
+        <v>3342.61</v>
+      </c>
+      <c r="G102" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>100005464447</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="E103" s="7" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="F103" s="7" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>100009711503</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="n">
+        <v>60769.39</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>60769.39</v>
+      </c>
+      <c r="F104" s="10" t="n">
+        <v>60769.39</v>
+      </c>
+      <c r="G104" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>100005502471</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="E105" s="7" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="F105" s="7" t="n"/>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>100009736962</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="n">
+        <v>143708.58</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>143708.58</v>
+      </c>
+      <c r="F106" s="10" t="n">
+        <v>143708.58</v>
+      </c>
+      <c r="G106" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>01-26070006</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="n">
+        <v>121915.63</v>
+      </c>
+      <c r="E107" s="7" t="n">
+        <v>121915.63</v>
+      </c>
+      <c r="F107" s="7" t="n">
+        <v>121915.63</v>
+      </c>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>01-26070005</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="n">
+        <v>96640.72</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>96640.72</v>
+      </c>
+      <c r="F108" s="10" t="n">
+        <v>96640.72</v>
+      </c>
+      <c r="G108" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>DJ82003461</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="n">
+        <v>20067.17</v>
+      </c>
+      <c r="E109" s="7" t="n">
+        <v>20067.17</v>
+      </c>
+      <c r="F109" s="7" t="n">
+        <v>20067.17</v>
+      </c>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>100005464401</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="F110" s="10" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="G110" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>FCO-000381</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="n">
+        <v>13934.55</v>
+      </c>
+      <c r="E111" s="7" t="n">
+        <v>13934.55</v>
+      </c>
+      <c r="F111" s="7" t="n">
+        <v>13934.55</v>
+      </c>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>1276114E</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="D112" s="10" t="n">
+        <v>2921.66</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>2921.66</v>
+      </c>
+      <c r="F112" s="10" t="n">
+        <v>2921.66</v>
+      </c>
+      <c r="G112" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>1276210E</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="n">
+        <v>4183.74</v>
+      </c>
+      <c r="E113" s="7" t="n">
+        <v>4183.74</v>
+      </c>
+      <c r="F113" s="7" t="n">
+        <v>4183.74</v>
+      </c>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>41480035S</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D114" s="10" t="n">
+        <v>1541.4</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>1541.4</v>
+      </c>
+      <c r="F114" s="10" t="n">
+        <v>1541.4</v>
+      </c>
+      <c r="G114" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>88290077</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="n">
+        <v>3454.11</v>
+      </c>
+      <c r="E115" s="7" t="n">
+        <v>3454.11</v>
+      </c>
+      <c r="F115" s="7" t="n">
+        <v>3454.11</v>
+      </c>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>88290076</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D116" s="10" t="n">
+        <v>1417.15</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>1417.15</v>
+      </c>
+      <c r="F116" s="10" t="n">
+        <v>1417.15</v>
+      </c>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>88288966</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="n">
+        <v>2400.87</v>
+      </c>
+      <c r="E117" s="7" t="n">
+        <v>2400.87</v>
+      </c>
+      <c r="F117" s="7" t="n">
+        <v>2400.87</v>
+      </c>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B118" s="9" t="inlineStr">
+        <is>
+          <t>88288967</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D118" s="10" t="n">
+        <v>2261.02</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>2261.02</v>
+      </c>
+      <c r="F118" s="10" t="n">
+        <v>2261.02</v>
+      </c>
+      <c r="G118" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>88288964</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="n">
+        <v>1166.17</v>
+      </c>
+      <c r="E119" s="7" t="n">
+        <v>1166.17</v>
+      </c>
+      <c r="F119" s="7" t="n">
+        <v>1166.17</v>
+      </c>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>88288968</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D120" s="10" t="n">
+        <v>1424.42</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>1424.42</v>
+      </c>
+      <c r="F120" s="10" t="n">
+        <v>1424.42</v>
+      </c>
+      <c r="G120" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>88288965</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="n">
+        <v>860.9400000000001</v>
+      </c>
+      <c r="E121" s="7" t="n">
+        <v>860.9400000000001</v>
+      </c>
+      <c r="F121" s="7" t="n">
+        <v>860.9400000000001</v>
+      </c>
+      <c r="G121" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>88289775</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D122" s="10" t="n">
+        <v>1092.94</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>1092.94</v>
+      </c>
+      <c r="F122" s="10" t="n">
+        <v>1092.94</v>
+      </c>
+      <c r="G122" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>88290078</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="n">
+        <v>634.8200000000001</v>
+      </c>
+      <c r="E123" s="7" t="n">
+        <v>634.8200000000001</v>
+      </c>
+      <c r="F123" s="7" t="n">
+        <v>634.8200000000001</v>
+      </c>
+      <c r="G123" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>88290075</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="n">
+        <v>1299.6</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>1299.6</v>
+      </c>
+      <c r="F124" s="10" t="n">
+        <v>1299.6</v>
+      </c>
+      <c r="G124" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>88289901</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="n">
+        <v>342.46</v>
+      </c>
+      <c r="E125" s="7" t="n">
+        <v>342.46</v>
+      </c>
+      <c r="F125" s="7" t="n">
+        <v>342.46</v>
+      </c>
+      <c r="G125" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>88289871</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D126" s="10" t="n">
+        <v>661.3200000000001</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>661.3200000000001</v>
+      </c>
+      <c r="F126" s="10" t="n">
+        <v>661.3200000000001</v>
+      </c>
+      <c r="G126" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>88289900</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="n">
+        <v>344.31</v>
+      </c>
+      <c r="E127" s="7" t="n">
+        <v>344.31</v>
+      </c>
+      <c r="F127" s="7" t="n">
+        <v>344.31</v>
+      </c>
+      <c r="G127" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>88289732</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D128" s="10" t="n">
+        <v>831.23</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>831.23</v>
+      </c>
+      <c r="F128" s="10" t="n">
+        <v>831.23</v>
+      </c>
+      <c r="G128" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>88289870</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="n">
+        <v>947.65</v>
+      </c>
+      <c r="E129" s="7" t="n">
+        <v>947.65</v>
+      </c>
+      <c r="F129" s="7" t="n">
+        <v>947.65</v>
+      </c>
+      <c r="G129" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>10258086507</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D130" s="10" t="n">
+        <v>114.64</v>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>114.64</v>
+      </c>
+      <c r="F130" s="10" t="n">
+        <v>114.64</v>
+      </c>
+      <c r="G130" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>10258087380</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="E131" s="7" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="F131" s="7" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="G131" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t>10258094336</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D132" s="10" t="n">
+        <v>340.43</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>340.43</v>
+      </c>
+      <c r="F132" s="10" t="n">
+        <v>340.43</v>
+      </c>
+      <c r="G132" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>10258092651</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="n">
+        <v>72.06</v>
+      </c>
+      <c r="E133" s="7" t="n">
+        <v>72.06</v>
+      </c>
+      <c r="F133" s="7" t="n">
+        <v>72.06</v>
+      </c>
+      <c r="G133" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B134" s="9" t="inlineStr">
+        <is>
+          <t>10258095440</t>
+        </is>
+      </c>
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D134" s="10" t="n">
+        <v>326.71</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>326.71</v>
+      </c>
+      <c r="F134" s="10" t="n">
+        <v>326.71</v>
+      </c>
+      <c r="G134" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>10258095586</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="n">
+        <v>124.79</v>
+      </c>
+      <c r="E135" s="7" t="n">
+        <v>124.79</v>
+      </c>
+      <c r="F135" s="7" t="n">
+        <v>124.79</v>
+      </c>
+      <c r="G135" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B136" s="9" t="inlineStr">
+        <is>
+          <t>10258094115</t>
+        </is>
+      </c>
+      <c r="C136" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D136" s="10" t="n">
+        <v>36.58</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>36.58</v>
+      </c>
+      <c r="F136" s="10" t="n"/>
+      <c r="G136" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>10258094230</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D137" s="7" t="n">
+        <v>171.72</v>
+      </c>
+      <c r="E137" s="7" t="n">
+        <v>171.72</v>
+      </c>
+      <c r="F137" s="7" t="n">
+        <v>171.72</v>
+      </c>
+      <c r="G137" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>10258093204</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D138" s="10" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="F138" s="10" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="G138" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>10258095791</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="n">
+        <v>115.6</v>
+      </c>
+      <c r="E139" s="7" t="n">
+        <v>115.6</v>
+      </c>
+      <c r="F139" s="7" t="n">
+        <v>115.6</v>
+      </c>
+      <c r="G139" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B140" s="9" t="inlineStr">
+        <is>
+          <t>10258095495</t>
+        </is>
+      </c>
+      <c r="C140" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D140" s="10" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="F140" s="10" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="G140" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>10258094804</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D141" s="7" t="n">
+        <v>195.18</v>
+      </c>
+      <c r="E141" s="7" t="n">
+        <v>195.18</v>
+      </c>
+      <c r="F141" s="7" t="n">
+        <v>195.18</v>
+      </c>
+      <c r="G141" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B142" s="9" t="inlineStr">
+        <is>
+          <t>10258092405</t>
+        </is>
+      </c>
+      <c r="C142" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D142" s="10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F142" s="10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G142" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>10258094916</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="E143" s="7" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="F143" s="7" t="n"/>
+      <c r="G143" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B144" s="9" t="inlineStr">
+        <is>
+          <t>10258094010</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D144" s="10" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="F144" s="10" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="G144" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>10258096185</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="n">
+        <v>279.25</v>
+      </c>
+      <c r="E145" s="7" t="n">
+        <v>279.25</v>
+      </c>
+      <c r="F145" s="7" t="n">
+        <v>279.25</v>
+      </c>
+      <c r="G145" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B146" s="9" t="inlineStr">
+        <is>
+          <t>10258094757</t>
+        </is>
+      </c>
+      <c r="C146" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D146" s="10" t="n">
+        <v>66.43000000000001</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>66.43000000000001</v>
+      </c>
+      <c r="F146" s="10" t="n">
+        <v>66.43000000000001</v>
+      </c>
+      <c r="G146" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>10258094955</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D147" s="7" t="n">
+        <v>144.31</v>
+      </c>
+      <c r="E147" s="7" t="n">
+        <v>144.31</v>
+      </c>
+      <c r="F147" s="7" t="n">
+        <v>144.31</v>
+      </c>
+      <c r="G147" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B148" s="9" t="inlineStr">
+        <is>
+          <t>10258094033</t>
+        </is>
+      </c>
+      <c r="C148" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D148" s="10" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="F148" s="10" t="n"/>
+      <c r="G148" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B149" s="6" t="inlineStr">
+        <is>
+          <t>10258089995</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="E149" s="7" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="F149" s="7" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="G149" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B150" s="9" t="inlineStr">
+        <is>
+          <t>10258093558</t>
+        </is>
+      </c>
+      <c r="C150" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D150" s="10" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="E150" s="10" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="F150" s="10" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="G150" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B151" s="6" t="inlineStr">
+        <is>
+          <t>10258085373</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D151" s="7" t="n">
+        <v>138.18</v>
+      </c>
+      <c r="E151" s="7" t="n">
+        <v>138.18</v>
+      </c>
+      <c r="F151" s="7" t="n"/>
+      <c r="G151" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B152" s="9" t="inlineStr">
+        <is>
+          <t>10258093923</t>
+        </is>
+      </c>
+      <c r="C152" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D152" s="10" t="n">
+        <v>635.09</v>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>635.09</v>
+      </c>
+      <c r="F152" s="10" t="n">
+        <v>635.09</v>
+      </c>
+      <c r="G152" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>10258093683</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D153" s="7" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="E153" s="7" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="F153" s="7" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="G153" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B154" s="9" t="inlineStr">
+        <is>
+          <t>10258093418</t>
+        </is>
+      </c>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D154" s="10" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="E154" s="10" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="F154" s="10" t="n"/>
+      <c r="G154" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B155" s="6" t="inlineStr">
+        <is>
+          <t>10258095368</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D155" s="7" t="n">
+        <v>362.77</v>
+      </c>
+      <c r="E155" s="7" t="n">
+        <v>362.77</v>
+      </c>
+      <c r="F155" s="7" t="n">
+        <v>362.77</v>
+      </c>
+      <c r="G155" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B156" s="9" t="inlineStr">
+        <is>
+          <t>10258094651</t>
+        </is>
+      </c>
+      <c r="C156" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D156" s="10" t="n">
+        <v>22.87</v>
+      </c>
+      <c r="E156" s="10" t="n">
+        <v>22.87</v>
+      </c>
+      <c r="F156" s="10" t="n">
+        <v>22.87</v>
+      </c>
+      <c r="G156" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="inlineStr">
+        <is>
+          <t>10258091193</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D157" s="7" t="n">
+        <v>39.06</v>
+      </c>
+      <c r="E157" s="7" t="n">
+        <v>39.06</v>
+      </c>
+      <c r="F157" s="7" t="n"/>
+      <c r="G157" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B158" s="9" t="inlineStr">
+        <is>
+          <t>10258096441</t>
+        </is>
+      </c>
+      <c r="C158" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D158" s="10" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="E158" s="10" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="F158" s="10" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="G158" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>10258094363</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D159" s="7" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="E159" s="7" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="F159" s="7" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="G159" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B160" s="9" t="inlineStr">
+        <is>
+          <t>10258095250</t>
+        </is>
+      </c>
+      <c r="C160" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D160" s="10" t="n">
+        <v>13.52</v>
+      </c>
+      <c r="E160" s="10" t="n">
+        <v>13.52</v>
+      </c>
+      <c r="F160" s="10" t="n"/>
+      <c r="G160" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t>10258091814</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D161" s="7" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="E161" s="7" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="F161" s="7" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="G161" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B162" s="9" t="inlineStr">
+        <is>
+          <t>10258095378</t>
+        </is>
+      </c>
+      <c r="C162" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D162" s="10" t="n">
+        <v>85.93000000000001</v>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>85.93000000000001</v>
+      </c>
+      <c r="F162" s="10" t="n">
+        <v>85.93000000000001</v>
+      </c>
+      <c r="G162" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
+        <is>
+          <t>10258092495</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D163" s="7" t="n">
+        <v>107.86</v>
+      </c>
+      <c r="E163" s="7" t="n">
+        <v>107.86</v>
+      </c>
+      <c r="F163" s="7" t="n"/>
+      <c r="G163" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B164" s="9" t="inlineStr">
+        <is>
+          <t>10258094178</t>
+        </is>
+      </c>
+      <c r="C164" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D164" s="10" t="n">
+        <v>55.78</v>
+      </c>
+      <c r="E164" s="10" t="n">
+        <v>55.78</v>
+      </c>
+      <c r="F164" s="10" t="n">
+        <v>55.78</v>
+      </c>
+      <c r="G164" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B165" s="6" t="inlineStr">
+        <is>
+          <t>10258093557</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D165" s="7" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="E165" s="7" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="F165" s="7" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="G165" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B166" s="9" t="inlineStr">
+        <is>
+          <t>10258094317</t>
+        </is>
+      </c>
+      <c r="C166" s="9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D166" s="10" t="n">
+        <v>19.01</v>
+      </c>
+      <c r="E166" s="10" t="n">
+        <v>19.01</v>
+      </c>
+      <c r="F166" s="10" t="n"/>
+      <c r="G166" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:G166"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CONTROLE FLUX FAC02 - FACTURES FOURNISSEURS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Fichier SRC</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>CEL01_SRC_FACTURESFOURNISSEURS_110826-200457_ST_CEL01_639220754971423753_001.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Fichier CTL</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>CEL01_CTL_FACTURESFOURNISSEURS_110826-200457_ST_CEL01_639220754971423753_001.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Resultat</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>RAPPROCHEMENT OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Folio</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Nb factures SRC</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Montant SRC</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Nb factures CTL</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Montant CTL</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>345233.41</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>345233.41</v>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>106</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>300322.87</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>106</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>300322.87</v>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>355909.93</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>355909.93</v>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>162</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>1001466.21</v>
+      </c>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="11" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:F9"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FACTURES A MONTANT ZERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Fichier source</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>CEL01_SRC_FACTURESFOURNISSEURS_110826-200457_ST_CEL01_639220754971423753_001.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Folio</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>N° facture</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Compte</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Date piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Aucune facture a montant 0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:D5"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CONTROLE FAC02 FOURNISSEURS - SYNTHESE ORACLE PAR FOLIO</t>
+        </is>
+      </c>
       <c r="B1" s="13" t="n"/>
       <c r="C1" s="13" t="n"/>
       <c r="D1" s="13" t="n"/>
       <c r="E1" s="13" t="n"/>
       <c r="F1" s="13" t="n"/>
       <c r="G1" s="13" t="n"/>
+      <c r="H1" s="13" t="n"/>
+      <c r="I1" s="13" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Fichier : CEL01_SRC_FACTURESFOURNISSEURS_110826-200457_ST_CEL01_639220754971423753_001  |  Execution : 25/08/2026 20:38:01</t>
+          <t>Fichier : CEL01_SRC_FACTURESFOURNISSEURS_110826-200457_ST_CEL01_639220754971423753_001  |  Execution : 26/08/2026 16:07:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Folio</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Fichier</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Nb Factures Fichier</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Montant Fichier</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Nb Factures Oracle</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Montant Oracle</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Nb Factures Interface</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Montant Interface</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>CEC</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>CEL01_SRC_FACTURESFOURNISSEURS_110826-200457_ST_CEL01_639220754971423753_001</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>345233.41</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>345233.41</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>341060.16</v>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>CEL01_SRC_FACTURESFOURNISSEURS_110826-200457_ST_CEL01_639220754971423753_001</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>106</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>300322.87</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>106</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>300322.87</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>276515.55</v>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>CEL01_SRC_FACTURESFOURNISSEURS_110826-200457_ST_CEL01_639220754971423753_001</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>355909.93</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>355909.93</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>355426.41</v>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>INTEGREE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:I7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G166"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CONTROLE FAC02 FOURNISSEURS - DETAIL FACTURE PAR FACTURE</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="n"/>
+      <c r="C1" s="13" t="n"/>
+      <c r="D1" s="13" t="n"/>
+      <c r="E1" s="13" t="n"/>
+      <c r="F1" s="13" t="n"/>
+      <c r="G1" s="13" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Fichier : CEL01_SRC_FACTURESFOURNISSEURS_110826-200457_ST_CEL01_639220754971423753_001  |  Execution : 26/08/2026 16:07:18</t>
         </is>
       </c>
     </row>
